--- a/research/traditional_assets/database/data/singapore/singapore_retail_online.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_retail_online.xlsx
@@ -587,23 +587,26 @@
           <t>Retail (Online)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.113</v>
+      </c>
       <c r="G2">
-        <v>-0.7694573453923247</v>
+        <v>-0.07765726681127984</v>
       </c>
       <c r="H2">
-        <v>-1.122923490589098</v>
+        <v>-0.07809110629067247</v>
       </c>
       <c r="I2">
-        <v>-1.364275238328037</v>
+        <v>-0.1248239487378955</v>
       </c>
       <c r="J2">
-        <v>-1.364275238328037</v>
+        <v>-0.1248239487378955</v>
       </c>
       <c r="K2">
-        <v>-2608.687</v>
+        <v>-2.58</v>
       </c>
       <c r="L2">
-        <v>-3.188324370569543</v>
+        <v>-0.1017550778939065</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,61 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3560.84</v>
+        <v>2.256</v>
       </c>
       <c r="V2">
-        <v>0.1334582647772035</v>
+        <v>0.3823728813559322</v>
+      </c>
+      <c r="W2">
+        <v>0.1625492550942422</v>
       </c>
       <c r="X2">
-        <v>0.0864152820737126</v>
+        <v>0.1427264686380047</v>
+      </c>
+      <c r="Y2">
+        <v>0.01982278645623753</v>
       </c>
       <c r="Z2">
-        <v>315.9073359073359</v>
+        <v>9.128528488990559</v>
+      </c>
+      <c r="AA2">
+        <v>-4.955457344511109</v>
       </c>
       <c r="AB2">
-        <v>0.07571784243084732</v>
+        <v>0.1269700564340024</v>
+      </c>
+      <c r="AC2">
+        <v>-5.082427400945111</v>
       </c>
       <c r="AD2">
-        <v>13949.913</v>
+        <v>1.122</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.02455610124669437</v>
       </c>
       <c r="AF2">
-        <v>13949.913</v>
+        <v>1.146556101246694</v>
       </c>
       <c r="AG2">
-        <v>10389.073</v>
+        <v>-1.109443898753305</v>
       </c>
       <c r="AH2">
-        <v>0.3433299665456702</v>
+        <v>0.1627115550877176</v>
       </c>
       <c r="AI2">
-        <v>2.020273388865371</v>
+        <v>0.515177353024004</v>
       </c>
       <c r="AJ2">
-        <v>0.2802527236507709</v>
+        <v>-0.2315897936075904</v>
       </c>
       <c r="AK2">
-        <v>3.106665933041338</v>
+        <v>36.4422411118698</v>
       </c>
       <c r="AL2">
-        <v>1672.035</v>
+        <v>0.102</v>
       </c>
       <c r="AM2">
-        <v>1611.035</v>
+        <v>0.102</v>
       </c>
       <c r="AN2">
-        <v>-18.04202459938696</v>
+        <v>-0.3945147679324895</v>
       </c>
       <c r="AO2">
-        <v>-0.6675996614903396</v>
+        <v>-31.23529411764705</v>
       </c>
       <c r="AP2">
-        <v>-13.43663653177097</v>
+        <v>0.3900998237529202</v>
       </c>
       <c r="AQ2">
-        <v>-0.6928775600778381</v>
+        <v>-31.23529411764705</v>
       </c>
     </row>
     <row r="3">
@@ -700,23 +715,26 @@
           <t>Retail (Online)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.113</v>
+      </c>
       <c r="G3">
-        <v>0.01378205128205128</v>
+        <v>-0.08069672131147541</v>
       </c>
       <c r="H3">
-        <v>0.007179487179487179</v>
+        <v>-0.08114754098360656</v>
       </c>
       <c r="I3">
-        <v>-0.04006410256410257</v>
+        <v>-0.1200819672131148</v>
       </c>
       <c r="J3">
-        <v>-0.04006410256410257</v>
+        <v>-0.1200819672131148</v>
       </c>
       <c r="K3">
-        <v>-0.6870000000000001</v>
+        <v>-2.34</v>
       </c>
       <c r="L3">
-        <v>-0.02201923076923077</v>
+        <v>-0.0959016393442623</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="V3">
-        <v>0.252054794520548</v>
+        <v>0.5259259259259259</v>
       </c>
       <c r="W3">
-        <v>-0.1962857142857143</v>
+        <v>-0.6015424164524421</v>
       </c>
       <c r="X3">
-        <v>0.0771354184265107</v>
+        <v>0.1392594469001015</v>
       </c>
       <c r="Y3">
-        <v>-0.273421132712225</v>
+        <v>-0.7408018633525436</v>
       </c>
       <c r="Z3">
-        <v>12.04633204633205</v>
+        <v>8.869501999272991</v>
       </c>
       <c r="AA3">
-        <v>-0.4826254826254827</v>
+        <v>-1.065067248273355</v>
       </c>
       <c r="AB3">
-        <v>0.07114079452424762</v>
+        <v>0.1277949588605917</v>
       </c>
       <c r="AC3">
-        <v>-0.5537662771497303</v>
+        <v>-1.192862207133947</v>
       </c>
       <c r="AD3">
-        <v>0.913</v>
+        <v>0.667</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.913</v>
+        <v>0.667</v>
       </c>
       <c r="AG3">
-        <v>-0.927</v>
+        <v>-1.463</v>
       </c>
       <c r="AH3">
-        <v>0.1111652258614392</v>
+        <v>0.1414034343862625</v>
       </c>
       <c r="AI3">
-        <v>0.1839613137215394</v>
+        <v>0.3077988001845871</v>
       </c>
       <c r="AJ3">
-        <v>-0.1454573983994979</v>
+        <v>-0.5655199072284499</v>
       </c>
       <c r="AK3">
-        <v>-0.2968299711815562</v>
+        <v>-39.54054054054038</v>
       </c>
       <c r="AL3">
-        <v>0.035</v>
+        <v>0.098</v>
       </c>
       <c r="AM3">
-        <v>0.035</v>
+        <v>0.098</v>
       </c>
       <c r="AN3">
-        <v>-0.7672268907563026</v>
+        <v>-0.232404181184669</v>
       </c>
       <c r="AO3">
-        <v>-35.71428571428571</v>
+        <v>-29.89795918367347</v>
       </c>
       <c r="AP3">
-        <v>0.7789915966386556</v>
+        <v>0.5097560975609755</v>
       </c>
       <c r="AQ3">
-        <v>-35.71428571428571</v>
+        <v>-29.89795918367347</v>
       </c>
     </row>
     <row r="4">
@@ -817,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited (NasdaqGS:GRAB)</t>
+          <t>New Momentum Corporation (OTCPK:NNAX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,22 +844,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.8005082592121983</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-1.167725540025413</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.416772554002541</v>
+        <v>-0.2459803353396219</v>
       </c>
       <c r="J4">
-        <v>-1.416772554002541</v>
+        <v>-0.2459803353396219</v>
       </c>
       <c r="K4">
-        <v>-2608</v>
+        <v>-0.24</v>
       </c>
       <c r="L4">
-        <v>-3.313850063532402</v>
+        <v>-0.2513089005235602</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,58 +883,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3559</v>
+        <v>0.126</v>
       </c>
       <c r="V4">
-        <v>0.1334258079028267</v>
+        <v>0.06810810810810811</v>
+      </c>
+      <c r="W4">
+        <v>0.9266409266409266</v>
       </c>
       <c r="X4">
-        <v>0.0956951457209145</v>
+        <v>0.1461934903759079</v>
+      </c>
+      <c r="Y4">
+        <v>0.7804474362650187</v>
+      </c>
+      <c r="Z4">
+        <v>35.96160411983956</v>
+      </c>
+      <c r="AA4">
+        <v>-8.845847440748862</v>
       </c>
       <c r="AB4">
-        <v>0.08029489033744702</v>
+        <v>0.1261451540074132</v>
+      </c>
+      <c r="AC4">
+        <v>-8.971992594756275</v>
       </c>
       <c r="AD4">
-        <v>13949</v>
+        <v>0.455</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.02455610124669437</v>
       </c>
       <c r="AF4">
-        <v>13949</v>
+        <v>0.4795561012466944</v>
       </c>
       <c r="AG4">
-        <v>10390</v>
+        <v>0.3535561012466944</v>
       </c>
       <c r="AH4">
-        <v>0.3433769047091549</v>
+        <v>0.2058572880000843</v>
       </c>
       <c r="AI4">
-        <v>2.021594202898551</v>
+        <v>8.189686318533138</v>
       </c>
       <c r="AJ4">
-        <v>0.2803259227282539</v>
+        <v>0.160447969101701</v>
       </c>
       <c r="AK4">
-        <v>3.109847351092487</v>
+        <v>-5.242225134995858</v>
       </c>
       <c r="AL4">
-        <v>1672</v>
+        <v>0.004</v>
       </c>
       <c r="AM4">
-        <v>1611</v>
+        <v>0.004</v>
       </c>
       <c r="AN4">
-        <v>-18.06865284974093</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>-0.6668660287081339</v>
+        <v>-64</v>
       </c>
       <c r="AP4">
-        <v>-13.45854922279793</v>
+        <v>13.59831158641132</v>
       </c>
       <c r="AQ4">
-        <v>-0.6921166977032899</v>
+        <v>-64</v>
       </c>
     </row>
   </sheetData>
